--- a/src/attributions/attributions_ig_traj_488.xlsx
+++ b/src/attributions/attributions_ig_traj_488.xlsx
@@ -1005,25 +1005,25 @@
         <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4667019280715205</v>
+        <v>-0.1497095656227148</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3846858995935022</v>
+        <v>0.1668763681846538</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.003582252589811255</v>
+        <v>-0.1031570271846702</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -1032,52 +1032,52 @@
         <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.1722340177876595</v>
+        <v>-0.06034494611418349</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3003288997905195</v>
+        <v>0.09820711477550953</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1258025001634858</v>
+        <v>-0.07381889687673504</v>
       </c>
       <c r="O2" t="n">
         <v>-0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R2" t="n">
         <v>-0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1955211877861541</v>
+        <v>-0.04675213381012092</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1747299438881934</v>
+        <v>0.1417554918566343</v>
       </c>
       <c r="W2" t="n">
-        <v>0.09528894210728789</v>
+        <v>0.04254945194057893</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -1086,19 +1086,19 @@
         <v>-0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.03046117376904777</v>
+        <v>0.004303299501309165</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.1311704012325126</v>
+        <v>-0.03044555570634951</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.1415786046774034</v>
+        <v>0.03408957103370139</v>
       </c>
       <c r="AG2" t="n">
         <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
@@ -1107,52 +1107,52 @@
         <v>-0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.09926097689252464</v>
+        <v>-0.1138918707675037</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.04285915125817542</v>
+        <v>0.2225392164316773</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.1438776405917472</v>
+        <v>-0.01915897255190865</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.565400520831479</v>
+        <v>-0.2790607507027192</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.5337497190590719</v>
+        <v>0.4014581575500772</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.2095207884692807</v>
+        <v>-0.2554352604970437</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA2" t="n">
         <v>-0</v>
@@ -1167,13 +1167,13 @@
         <v>-0</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.09518065818777773</v>
+        <v>-0.008378129901397734</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.08220195497852749</v>
+        <v>-0.2528962020124512</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.0877438747651834</v>
+        <v>-0.05180024067167283</v>
       </c>
       <c r="BH2" t="n">
         <v>-0</v>
@@ -1182,25 +1182,25 @@
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
         <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.1556862342842459</v>
+        <v>0.08406876570901749</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.001052533246369743</v>
+        <v>0.06693856594977407</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.3320239254885698</v>
+        <v>0.1570825927398987</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
@@ -1209,58 +1209,58 @@
         <v>-0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0.1345838722570084</v>
+        <v>-0.05311358083608007</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.277883395820325</v>
+        <v>0.27168195016915</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.08309917184448994</v>
+        <v>-0.0568674285594116</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA2" t="n">
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
         <v>0</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.2002959211098397</v>
+        <v>0.1008284698621818</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.1909381532689066</v>
+        <v>-0.09252989043066026</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.06261268834534339</v>
+        <v>0.02577575037997117</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK2" t="n">
         <v>-0</v>
@@ -1269,55 +1269,55 @@
         <v>0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.00340871230383861</v>
+        <v>0.07486646963384312</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.05450664776826945</v>
+        <v>0.03242496576187809</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.08748810957717083</v>
+        <v>0.005362902528960502</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW2" t="n">
         <v>-0</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.1436172153640564</v>
+        <v>0.08867532472987356</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.1630882962991448</v>
+        <v>-0.09823616272128974</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.0935114647842145</v>
+        <v>0.0489606235716332</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
         <v>-0</v>
@@ -1326,106 +1326,106 @@
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.006283371112204082</v>
+        <v>0.03578649628866098</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0.1845655539266625</v>
+        <v>-0.1112200270566126</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.0344778031231453</v>
+        <v>0.004880190556414111</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM2" t="n">
         <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
         <v>0</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.1238990717651996</v>
+        <v>0.01758006984862974</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0.07744327120497345</v>
+        <v>-0.07706727541372722</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.06117069747894206</v>
+        <v>0.03107262888205512</v>
       </c>
       <c r="DS2" t="n">
         <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV2" t="n">
         <v>-0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.08509769100650146</v>
+        <v>-0.05432766616557193</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.1542392024545403</v>
+        <v>-0.09538452787900988</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.1603254615404854</v>
+        <v>-0.03446545069818886</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
         <v>-0</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.2231137695950056</v>
+        <v>0.02902555489484664</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0.215130922500245</v>
+        <v>-0.02816652106034484</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.04953040079865403</v>
+        <v>-0.05678403067163708</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
         <v>0</v>
@@ -1434,19 +1434,19 @@
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.1304107439810908</v>
+        <v>-0.01129627108547452</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.1442514037217011</v>
+        <v>-0.1116226039397727</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.01291112092219768</v>
+        <v>0.06780868015972789</v>
       </c>
       <c r="ET2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU2" t="n">
         <v>-0</v>
@@ -1458,28 +1458,28 @@
         <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY2" t="n">
         <v>0</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.1694850667261793</v>
+        <v>0.07802427177403651</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.1777095251294548</v>
+        <v>-0.09972652526084519</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.06889265909546738</v>
+        <v>0.02952054589029818</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
         <v>0</v>
@@ -1488,25 +1488,25 @@
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.1669803342648943</v>
+        <v>0.1515985688960327</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.1565013211177333</v>
+        <v>-0.1087111493766292</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.1418555982618243</v>
+        <v>-0.0138840110361984</v>
       </c>
       <c r="FL2" t="n">
         <v>0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
         <v>0</v>
@@ -1515,16 +1515,16 @@
         <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.03468145562072295</v>
+        <v>0.007107592123056419</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.01794149478629247</v>
+        <v>0.002882809052208903</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.2265169175760449</v>
+        <v>0.04227429916334437</v>
       </c>
       <c r="FU2" t="n">
         <v>-0</v>
@@ -1533,28 +1533,28 @@
         <v>0</v>
       </c>
       <c r="FW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
         <v>-0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0.01558561635337</v>
+        <v>0.1141623281981366</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0.02981174926990749</v>
+        <v>-0.14522660096624</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>0</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="GG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -2140,25 +2140,25 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.05701928126257337</v>
+        <v>0.446724617983664</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04407182797653815</v>
+        <v>0.06166403910237639</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.02356865129619731</v>
+        <v>-0.2325999198121644</v>
       </c>
       <c r="G4" t="n">
         <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02521483631858222</v>
+        <v>0.4063889362853937</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,13 +2176,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.03335718290725152</v>
+        <v>-0.0591586014979687</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.01338430840234112</v>
+        <v>-0.1349440135476362</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-0</v>
@@ -2191,10 +2191,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007750520804463668</v>
+        <v>0.1801923630295364</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2203,52 +2203,52 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.00946905416050089</v>
+        <v>-0.1626259935434811</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01514579351294725</v>
+        <v>-0.021118514752988</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01867839133153118</v>
+        <v>-0.004004972176248329</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.01147479669104865</v>
+        <v>-0.2319754643547717</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.007771376837378263</v>
+        <v>-0.0239720655934386</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01693344895480376</v>
+        <v>0.1825313974778585</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.0155045050644903</v>
+        <v>0.06891105618466137</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.006252562440634738</v>
+        <v>-0.1581842673328484</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>-0</v>
@@ -2272,37 +2272,37 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.07302266781353239</v>
+        <v>0.7963841353987946</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.03472502549991104</v>
+        <v>-0.2053673014158674</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.02155954503824335</v>
+        <v>-0.2890807066656658</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.02903506985319622</v>
+        <v>-0.006797331707108151</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,43 +2311,43 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.03843536854050697</v>
+        <v>-0.09637936912474092</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.01987844475699061</v>
+        <v>-0.1966043123830153</v>
       </c>
       <c r="BI4" t="n">
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.03595536901831537</v>
+        <v>0.05730865562381634</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.01362467336988746</v>
+        <v>0.1140407912882945</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.007473438273061599</v>
+        <v>0.1535981234613757</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.02543298418951691</v>
+        <v>0.4155432619339144</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,64 +2365,64 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.01677302946842314</v>
+        <v>-0.03455512040335559</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0024270047197002</v>
+        <v>-0.1180352105892841</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>-0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.01076807114662567</v>
+        <v>-0.2155244672255784</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.01486242951194978</v>
+        <v>-0.05152452805188165</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.01205057764137815</v>
+        <v>0.1715716595166735</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.001814848595457616</v>
+        <v>-0.1520335699655763</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
         <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.002430282152926176</v>
+        <v>0.07867468031888633</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.002777843255539224</v>
+        <v>0.07835953350192745</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2431,31 +2431,31 @@
         <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.003807222770311498</v>
+        <v>-0.2082984491294397</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
         <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.01354095255662185</v>
+        <v>-0.05053279265342665</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0146221800155275</v>
+        <v>0.1770838060445039</v>
       </c>
       <c r="DB4" t="n">
         <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
         <v>0</v>
@@ -2464,52 +2464,52 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.00933429878654863</v>
+        <v>-0.1320170223948071</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01163541764634889</v>
+        <v>-0.147772288427828</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.004188768464337353</v>
+        <v>0.06645247090266659</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.0072717373642185</v>
+        <v>-0.09565501236775253</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01376330371396027</v>
+        <v>-0.022373010987019</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.0173251076104598</v>
+        <v>0.01743987108603649</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>-0</v>
@@ -2518,25 +2518,25 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.002880428846939636</v>
+        <v>-0.01758498090760462</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.02261259468521298</v>
+        <v>-0.005473218847237241</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.00433899442152498</v>
+        <v>0.1339185707302705</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
         <v>-0</v>
@@ -2545,34 +2545,34 @@
         <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.004245760345035532</v>
+        <v>-0.08342312846524116</v>
       </c>
       <c r="EH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.006724415804546999</v>
+        <v>-0.1216152467718849</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.004764687746619129</v>
+        <v>0.03051887692535797</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.00883050400624898</v>
+        <v>-0.1277750972678055</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
@@ -2581,79 +2581,79 @@
         <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.009932941636039836</v>
+        <v>-0.1746138572807248</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0157164408972182</v>
+        <v>0.1710567391446354</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.002033576997858147</v>
+        <v>-0.2280780938766459</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.01320970812715461</v>
+        <v>-0.09219640896553381</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.01551748291654144</v>
+        <v>0.1449402771436536</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
         <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01543354656530218</v>
+        <v>-0.282728439827745</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.02467438383705136</v>
+        <v>0.05172973952080046</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.008257416342651001</v>
+        <v>0.2103071173473222</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.001789525256754446</v>
+        <v>0.03671536473771458</v>
       </c>
       <c r="FR4" t="n">
         <v>0</v>
@@ -2662,25 +2662,25 @@
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0004865640967654394</v>
+        <v>0.01179400577589267</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.02145911507506609</v>
+        <v>0.01768127306462748</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.01797734213028336</v>
+        <v>-0.06999331981538022</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
@@ -2692,10 +2692,10 @@
         <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.003821323732838951</v>
+        <v>0.1142849291176853</v>
       </c>
       <c r="GE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF4" t="n">
         <v>0</v>
@@ -2709,16 +2709,16 @@
         <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.2711279876445548</v>
+        <v>-0.3128433349318569</v>
       </c>
       <c r="C5" t="n">
         <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2360533058946559</v>
+        <v>0.3030354986499976</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2139734129814401</v>
+        <v>0.142278371743065</v>
       </c>
       <c r="F5" t="n">
         <v>-0</v>
@@ -2736,25 +2736,25 @@
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1551849371544326</v>
+        <v>-0.2366043729694733</v>
       </c>
       <c r="L5" t="n">
         <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.155506031209121</v>
+        <v>0.3208120840883791</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1379087358836497</v>
+        <v>0.1545311869496546</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R5" t="n">
         <v>-0</v>
@@ -2763,49 +2763,49 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.09097600018001741</v>
+        <v>-0.1088962610326259</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0824375452024025</v>
+        <v>0.05612888309249404</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.007735876140625754</v>
+        <v>0.001462911821464024</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.04855375770294777</v>
+        <v>-0.03705769189241601</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.02941810738279912</v>
+        <v>0.1315746576765649</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.08126887332351614</v>
+        <v>-0.1491401780026298</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -2817,25 +2817,25 @@
         <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.130831201657047</v>
+        <v>-0.3059231384596314</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.05053275657742139</v>
+        <v>0.122404701833477</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.100925704105441</v>
+        <v>-0.3536404625198885</v>
       </c>
       <c r="AP5" t="n">
         <v>-0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
@@ -2844,22 +2844,22 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.4144201778092566</v>
+        <v>-0.556939576163867</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.2058904002611072</v>
+        <v>0.2660544425216219</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1990334133778029</v>
+        <v>0.1129303605937284</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
         <v>-0</v>
@@ -2871,25 +2871,25 @@
         <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.02031282361567278</v>
+        <v>0.1870391674453943</v>
       </c>
       <c r="BE5" t="n">
         <v>-0</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.126187556725891</v>
+        <v>0.04506969686969718</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.2229021620660003</v>
+        <v>0.25952336035027</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI5" t="n">
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>-0</v>
@@ -2898,22 +2898,22 @@
         <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.06840188800874134</v>
+        <v>0.09545202979021893</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.01975495362833976</v>
+        <v>-0.03953471942774767</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.03184273537806377</v>
+        <v>0.06122350712394787</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,19 +2925,19 @@
         <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.2182241505082316</v>
+        <v>-0.4170587165446679</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.1229669097238407</v>
+        <v>0.1874535412281457</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.07092651312569997</v>
+        <v>0.06378717751010722</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>0</v>
@@ -2946,22 +2946,22 @@
         <v>-0</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD5" t="n">
         <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0754443892768011</v>
+        <v>0.2857247309450462</v>
       </c>
       <c r="CF5" t="n">
         <v>0</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.03785508653058389</v>
+        <v>-0.1876012320440176</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.02876667069320623</v>
+        <v>0.01440821733563566</v>
       </c>
       <c r="CI5" t="n">
         <v>0</v>
@@ -2979,19 +2979,19 @@
         <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.04981061535821817</v>
+        <v>0.1929275047925429</v>
       </c>
       <c r="CO5" t="n">
         <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.05835089133120162</v>
+        <v>-0.1730552903528946</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.01181479047537486</v>
+        <v>-0.0678889340983643</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS5" t="n">
         <v>0</v>
@@ -3003,19 +3003,19 @@
         <v>0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.08200553931066712</v>
+        <v>0.2817591205051662</v>
       </c>
       <c r="CX5" t="n">
         <v>-0</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.05057562600433908</v>
+        <v>-0.1934891633799789</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.04763269232209195</v>
+        <v>-0.01484220822988207</v>
       </c>
       <c r="DA5" t="n">
         <v>-0</v>
@@ -3033,19 +3033,19 @@
         <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.06547273472598375</v>
+        <v>0.214735715855105</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.02403842520580389</v>
+        <v>-0.04643937337516522</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.002678548013210618</v>
+        <v>0.1147836551640251</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3057,19 +3057,19 @@
         <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.1143853038298592</v>
+        <v>0.1033022030307285</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.03754306133521421</v>
+        <v>-0.06345305204273231</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.1045555432265196</v>
+        <v>0.05656157134732072</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
@@ -3084,25 +3084,25 @@
         <v>-0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.007862213606053001</v>
+        <v>-0.09734729869118541</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0341080465801702</v>
+        <v>0.05276031248054343</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.01553298184274903</v>
+        <v>-0.190928199067654</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
@@ -3114,25 +3114,25 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.00793261205834106</v>
+        <v>0.266353053274813</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.08078721334955653</v>
+        <v>-0.1687267906081955</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.1109049602410694</v>
+        <v>-0.07817124452179394</v>
       </c>
       <c r="EK5" t="n">
         <v>0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
         <v>0</v>
@@ -3141,22 +3141,22 @@
         <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.06865838686327114</v>
+        <v>0.1908272167402858</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.006069160077645026</v>
+        <v>-0.1382468635587462</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.09787592393761449</v>
+        <v>-0.09748957555094191</v>
       </c>
       <c r="ET5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
         <v>-0</v>
@@ -3168,22 +3168,22 @@
         <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.08076221202348834</v>
+        <v>0.3363484552117071</v>
       </c>
       <c r="EZ5" t="n">
         <v>0</v>
       </c>
       <c r="FA5" t="n">
-        <v>-0.07945088655796798</v>
+        <v>-0.2293846621001945</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.02813799982353132</v>
+        <v>-0.01457295159368968</v>
       </c>
       <c r="FC5" t="n">
         <v>0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3195,46 +3195,46 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0277205883919439</v>
+        <v>0.187155279576142</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.03497800049707257</v>
+        <v>-0.1171285754431142</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.04981604869361134</v>
+        <v>-0.02731955359410795</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN5" t="n">
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP5" t="n">
         <v>0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.00244238115912955</v>
+        <v>-0.01181614271542909</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>-0.0985435748813578</v>
+        <v>-0.08065551520971657</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.001443396607080473</v>
+        <v>-0.01179497290594811</v>
       </c>
       <c r="FU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV5" t="n">
         <v>0</v>
@@ -3243,19 +3243,19 @@
         <v>-0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.01320609026703053</v>
+        <v>0.2739992407384946</v>
       </c>
       <c r="GA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.0265515259252674</v>
+        <v>-0.145466746341143</v>
       </c>
       <c r="GC5" t="n">
         <v>-0</v>
@@ -3278,43 +3278,43 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4983968840139405</v>
+        <v>0.3604057409234553</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1960818227080932</v>
+        <v>-0.2785397013317374</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1340491263732326</v>
+        <v>0.08797310921357238</v>
       </c>
       <c r="F6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3933200085796679</v>
+        <v>0.3600538255655048</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1239171608252099</v>
+        <v>-0.2163782927131096</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1356498282216958</v>
+        <v>0.04658681691272817</v>
       </c>
       <c r="O6" t="n">
         <v>-0</v>
@@ -3332,19 +3332,19 @@
         <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1211826115375206</v>
+        <v>0.06619316939376525</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01095062510312352</v>
+        <v>-0.03274277515602217</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1292355755413719</v>
+        <v>-0.1303828939563358</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
@@ -3353,28 +3353,28 @@
         <v>-0</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2145290972688035</v>
+        <v>0.1383620915310121</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.01043596495082893</v>
+        <v>-0.08976088091137779</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.04302476753102772</v>
+        <v>-0.193806823978149</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
@@ -3383,46 +3383,46 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.01027778191419253</v>
+        <v>0.2530478168768155</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.08596980347090974</v>
+        <v>-0.1068056640545205</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.12243702146784</v>
+        <v>0.04906026014784034</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.6058274128564402</v>
+        <v>0.3924972068635012</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.06868592794873193</v>
+        <v>-0.1181860844073677</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.04564711082150145</v>
+        <v>-0.146363921866385</v>
       </c>
       <c r="AY6" t="n">
         <v>-0</v>
@@ -3440,16 +3440,16 @@
         <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.1483809576332202</v>
+        <v>-0.005859445698918653</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.07806925391885007</v>
+        <v>-0.09566695328635751</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.08846264585331852</v>
+        <v>-0.0700505154715132</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -3467,16 +3467,16 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.1333130321339134</v>
+        <v>0.01804509057280179</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.05642358230947121</v>
+        <v>0.08592077658506862</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.2431474176461969</v>
+        <v>0.05588453889883547</v>
       </c>
       <c r="BQ6" t="n">
         <v>-0</v>
@@ -3494,49 +3494,49 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.2655376010211759</v>
+        <v>0.2384371486717977</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.01386405303996211</v>
+        <v>-0.1156002323066782</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.09254182175893665</v>
+        <v>0.008843427423850764</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.1281870918071553</v>
+        <v>-0.2016494767960739</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.02533457435841729</v>
+        <v>0.2200365598884417</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.02706250577385388</v>
+        <v>-0.04763757585924158</v>
       </c>
       <c r="CI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3548,25 +3548,25 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.09953865882393335</v>
+        <v>-0.117654040865157</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.1079579257310274</v>
+        <v>0.4266414419752668</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.1424554843724411</v>
+        <v>0.06810123646874298</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
         <v>-0</v>
@@ -3575,25 +3575,25 @@
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.1141336217733712</v>
+        <v>-0.1818370440048685</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.04208438202404405</v>
+        <v>0.2087367797153409</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.01777326761555184</v>
+        <v>-0.04210934432853009</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
@@ -3602,43 +3602,43 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.01228429709374339</v>
+        <v>0.05441748795021601</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.1776468562669744</v>
+        <v>0.03784836446039943</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.01381009069896385</v>
+        <v>-0.07890500375696384</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.130575598739882</v>
+        <v>-0.1936723748843055</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.1140455576315816</v>
+        <v>0.1841398824180874</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.1055108489354035</v>
+        <v>0.01730871904659783</v>
       </c>
       <c r="DS6" t="n">
         <v>-0</v>
@@ -3647,79 +3647,79 @@
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.176030720148956</v>
+        <v>-0.1495519682231477</v>
       </c>
       <c r="DY6" t="n">
         <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.04752365240029822</v>
+        <v>-0.1413070172539429</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.07870372961090372</v>
+        <v>-0.1222785944010389</v>
       </c>
       <c r="EB6" t="n">
         <v>0</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.1207310531500281</v>
+        <v>-0.02977690860972917</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.1173638690234988</v>
+        <v>0.1404211739330517</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.1892873251444971</v>
+        <v>0.01038686973650749</v>
       </c>
       <c r="EK6" t="n">
         <v>-0</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.1205206906531203</v>
+        <v>-0.2036384157230767</v>
       </c>
       <c r="EQ6" t="n">
         <v>0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0339314158934968</v>
+        <v>0.1146674010256109</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.09209771468745467</v>
+        <v>0.008906699316509899</v>
       </c>
       <c r="ET6" t="n">
         <v>-0</v>
@@ -3728,25 +3728,25 @@
         <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.1125613003437676</v>
+        <v>-0.2123555261738136</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.04872843462208998</v>
+        <v>0.2370391852821808</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.04773965018940341</v>
+        <v>-0.05372479426343821</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
@@ -3755,25 +3755,25 @@
         <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF6" t="n">
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.1960593038356874</v>
+        <v>-0.1204558697832805</v>
       </c>
       <c r="FI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.05314042000316321</v>
+        <v>0.06779881312093826</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.0954602950584733</v>
+        <v>-0.3317584458623004</v>
       </c>
       <c r="FL6" t="n">
         <v>-0</v>
@@ -3782,28 +3782,28 @@
         <v>-0</v>
       </c>
       <c r="FN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
         <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.02940615222200384</v>
+        <v>-0.04348059761236453</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>-0.03638503545686785</v>
+        <v>-0.03279345715858498</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.09063597326374805</v>
+        <v>0.04415975010635115</v>
       </c>
       <c r="FU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV6" t="n">
         <v>0</v>
@@ -3818,60 +3818,60 @@
         <v>-0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.08553080704328381</v>
+        <v>-0.07430755908994677</v>
       </c>
       <c r="GA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0.06801081502832355</v>
+        <v>0.2782573097228013</v>
       </c>
       <c r="GC6" t="n">
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.2070634505277382</v>
+        <v>0.1211407281720874</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C7" t="n">
         <v>-0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1527891103966427</v>
+        <v>-0.2259700204880312</v>
       </c>
       <c r="E7" t="n">
-        <v>0.139728663288919</v>
+        <v>0.06119051836944039</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1917258400045113</v>
+        <v>0.07345480424804739</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -3880,25 +3880,25 @@
         <v>-0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.04985037874858319</v>
+        <v>-0.2489647685771842</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07265805899522786</v>
+        <v>0.01180178171278852</v>
       </c>
       <c r="O7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03951392609810863</v>
+        <v>-0.02075182520075773</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -3907,91 +3907,91 @@
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1158493505250817</v>
+        <v>-0.04601566016430563</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07559995758532403</v>
+        <v>-0.05899608221467662</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>-0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.07514302565019154</v>
+        <v>0.03836159916892905</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.05468898661808234</v>
+        <v>0.05814216846345032</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.03315903206327819</v>
+        <v>0.1747435259538449</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.03081981300858528</v>
+        <v>0.03270711358065359</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.02821140374572752</v>
+        <v>-0.1404576521224002</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.06527354417435588</v>
+        <v>0.04789065645693523</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
         <v>-0</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.1507135222550541</v>
+        <v>-0.06397084095699487</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.06687335919845093</v>
+        <v>-0.3505869526169145</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.2616230709455466</v>
+        <v>-0.02230971754025507</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
@@ -4006,7 +4006,7 @@
         <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.2190484409978439</v>
+        <v>0.1661245603880065</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
@@ -4015,37 +4015,37 @@
         <v>-0</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.01422336449566378</v>
+        <v>0.2068981614639333</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.05924868341714198</v>
+        <v>0.1684847092327525</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.08814029639012623</v>
+        <v>-0.003613179619675863</v>
       </c>
       <c r="BM7" t="n">
         <v>0</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.03412363422752315</v>
+        <v>0.01389766238075032</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1706622831733927</v>
+        <v>-0.1089563399075943</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
@@ -4054,25 +4054,25 @@
         <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0465102087152437</v>
+        <v>-0.04801164201136012</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW7" t="n">
         <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.007585108612994046</v>
+        <v>-0.1967194947099738</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.110756428040185</v>
+        <v>-0.03917618133221584</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -4081,13 +4081,13 @@
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0.03724474927715508</v>
+        <v>-0.05510357444304977</v>
       </c>
       <c r="CE7" t="n">
         <v>0</v>
@@ -4096,16 +4096,16 @@
         <v>0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.02055046533162123</v>
+        <v>0.1077389389097189</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0429480442387252</v>
+        <v>-0.02004315818429219</v>
       </c>
       <c r="CI7" t="n">
         <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
@@ -4114,61 +4114,61 @@
         <v>-0</v>
       </c>
       <c r="CM7" t="n">
-        <v>-0.05572466906644654</v>
+        <v>-0.0008004771742731702</v>
       </c>
       <c r="CN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.1332427231054665</v>
+        <v>0.1108377789218846</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1162277573287646</v>
+        <v>-0.04935645159439225</v>
       </c>
       <c r="CR7" t="n">
         <v>0</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
         <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0.01667374347957047</v>
+        <v>-0.04688053165691792</v>
       </c>
       <c r="CW7" t="n">
         <v>-0</v>
       </c>
       <c r="CX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.006332038206917859</v>
+        <v>0.1095484196360995</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.03487417398405242</v>
+        <v>-0.001650573257281331</v>
       </c>
       <c r="DA7" t="n">
         <v>-0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0.02163093039542517</v>
+        <v>-0.00356116194881815</v>
       </c>
       <c r="DF7" t="n">
         <v>-0</v>
@@ -4177,10 +4177,10 @@
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.07475444571538935</v>
+        <v>0.08129640828805447</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.03584592152099914</v>
+        <v>-0.01676680481950708</v>
       </c>
       <c r="DJ7" t="n">
         <v>0</v>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0.0502686641409219</v>
+        <v>-0.06579225939158799</v>
       </c>
       <c r="DO7" t="n">
         <v>-0</v>
@@ -4204,70 +4204,70 @@
         <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0689678159436011</v>
+        <v>0.01358216993179534</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.1076274657611254</v>
+        <v>0.01236702613106507</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>-0.07151857677275862</v>
+        <v>0.01347315508193833</v>
       </c>
       <c r="DX7" t="n">
         <v>-0</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.02347601385324561</v>
+        <v>0.01324501646482771</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.08979990174464668</v>
+        <v>0.02690201716855667</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0.03874323153515925</v>
+        <v>-0.08607162868138776</v>
       </c>
       <c r="EG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.02977845107568349</v>
+        <v>0.09918299477684325</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.01780462056955368</v>
+        <v>0.02006589166306759</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
@@ -4276,22 +4276,22 @@
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.01243484029829679</v>
+        <v>0.0279013410814376</v>
       </c>
       <c r="EP7" t="n">
         <v>0</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.03368536203129598</v>
+        <v>0.1194958974062769</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.01847656782168937</v>
+        <v>0.01951838139490126</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
         <v>0</v>
@@ -4303,34 +4303,34 @@
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>-0.02151086311395828</v>
+        <v>-0.05383611330695823</v>
       </c>
       <c r="EY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0.01032136593724652</v>
+        <v>0.1409603175517452</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.04605219388245954</v>
+        <v>-0.01163953021819537</v>
       </c>
       <c r="FC7" t="n">
         <v>0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0.0426524212475698</v>
+        <v>0.01690408517940004</v>
       </c>
       <c r="FH7" t="n">
         <v>0</v>
@@ -4339,10 +4339,10 @@
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.02823741710139682</v>
+        <v>0.09958957096224487</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.1862454436008055</v>
+        <v>0.1305197848836541</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
@@ -4351,13 +4351,13 @@
         <v>-0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
         <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.007815398110875709</v>
+        <v>-0.006106269398164259</v>
       </c>
       <c r="FQ7" t="n">
         <v>-0</v>
@@ -4366,34 +4366,34 @@
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.0285089755736265</v>
+        <v>0.2291507346583974</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.07697554240654686</v>
+        <v>0.07460672935131413</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW7" t="n">
         <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.03651876679948103</v>
+        <v>0.01987395830541937</v>
       </c>
       <c r="FZ7" t="n">
         <v>0</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.0508204063516501</v>
+        <v>0.1903930481415776</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
@@ -5554,22 +5554,22 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.559524000778469</v>
+        <v>0.3129544858893787</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2330714662812555</v>
+        <v>-0.1522348581145022</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.02770239934542904</v>
+        <v>-0.06054775312193345</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5581,22 +5581,22 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3230855615148865</v>
+        <v>0.2967024060103832</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2397277187806909</v>
+        <v>-0.2015315886581548</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.02953011226699564</v>
+        <v>-0.1093389791354686</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -5608,76 +5608,76 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.120066479444405</v>
+        <v>0.03975427820473097</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.001989388732499831</v>
+        <v>-0.05146555047132426</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1981399025553424</v>
+        <v>-0.07338353732334585</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.09296925325541129</v>
+        <v>-0.0722500547200715</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.05401021876134467</v>
+        <v>-0.09776391800451797</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.06264986771571722</v>
+        <v>-0.06291256572592854</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.01235659805607243</v>
+        <v>0.0969240921655647</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.06100369606455219</v>
+        <v>-0.09965126744366093</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0002119291363684451</v>
+        <v>0.05204442113764492</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
@@ -5689,25 +5689,25 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.5098456828529349</v>
+        <v>0.2657099499193543</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.09552904747648819</v>
+        <v>-0.0600998929872754</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1819136161770179</v>
+        <v>-0.1597602810296587</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,25 +5716,25 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.08121509447588829</v>
+        <v>-0.006391949691019367</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.2667270040379431</v>
+        <v>-0.02478779232793465</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.186434618143963</v>
+        <v>-0.04449380173021578</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,70 +5743,70 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.1251908454217623</v>
+        <v>-0.01179273096250095</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>-0.003148522337728738</v>
+        <v>0.05499549609912618</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.2043354629318599</v>
+        <v>0.04739752902133432</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
         <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1528064659880441</v>
+        <v>0.1456380305265589</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.03774634467414721</v>
+        <v>-0.09647464657329732</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.1017985922537798</v>
+        <v>-0.02685765196501011</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.1252460441192026</v>
+        <v>-0.1065988158494016</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0.005043077300149587</v>
+        <v>0.09202045237825149</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.02220350025576284</v>
+        <v>0.01385107251609353</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
@@ -5818,25 +5818,25 @@
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.001641613671571868</v>
+        <v>-0.06153989477416343</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.234997905177404</v>
+        <v>0.1632184907034185</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.08469055862311795</v>
+        <v>0.03710302634963917</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
@@ -5851,43 +5851,43 @@
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.0891056202446842</v>
+        <v>-0.106157982701392</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.03755195343861334</v>
+        <v>0.09937784504360463</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.03639352869303281</v>
+        <v>0.02520446763208374</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.02845429717720982</v>
+        <v>-0.04766276393289846</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.08827535161278906</v>
+        <v>0.02720481866004532</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.04361921855614237</v>
+        <v>-0.08619502799551179</v>
       </c>
       <c r="DJ10" t="n">
         <v>-0</v>
@@ -5902,28 +5902,28 @@
         <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.08181816000405309</v>
+        <v>-0.05702110941019668</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.02359114695772073</v>
+        <v>-0.0267844321647682</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.04949029273662999</v>
+        <v>-0.02575022804124076</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
@@ -5932,16 +5932,16 @@
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.05132575569395859</v>
+        <v>-0.002414347075065819</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.0520147183943462</v>
+        <v>0.07028128159804879</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.08288540225719272</v>
+        <v>-0.0007819913975252653</v>
       </c>
       <c r="EB10" t="n">
         <v>-0</v>
@@ -5950,52 +5950,52 @@
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.1034471576652698</v>
+        <v>-0.08158634206860667</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0.02708120228071764</v>
+        <v>0.06665113387132716</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.08740387655414349</v>
+        <v>0.06338811704014582</v>
       </c>
       <c r="EK10" t="n">
         <v>0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
         <v>0</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.009553618274564005</v>
+        <v>-0.04153981445491703</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.01987120470674911</v>
+        <v>0.06431711266781782</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01159875883617959</v>
+        <v>-0.004923844471995725</v>
       </c>
       <c r="ET10" t="n">
         <v>0</v>
@@ -6013,25 +6013,25 @@
         <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.0855048522954759</v>
+        <v>-0.1121471316519863</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0.02447884065062331</v>
+        <v>0.1187886044090597</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.003702749208864165</v>
+        <v>0.006023998426831777</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF10" t="n">
         <v>0</v>
@@ -6040,16 +6040,16 @@
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.01479937446324157</v>
+        <v>0.1073044837231265</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.008459869775285591</v>
+        <v>0.07366274000973731</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.02279557559513727</v>
+        <v>0.01470913974689237</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
@@ -6061,28 +6061,28 @@
         <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.04621183659143154</v>
+        <v>0.04378216511573787</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.03337502380121125</v>
+        <v>0.1042751487820166</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.05881057984368338</v>
+        <v>-0.01968128517293833</v>
       </c>
       <c r="FU10" t="n">
         <v>-0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
         <v>-0</v>
@@ -6091,25 +6091,25 @@
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.07406946616481051</v>
+        <v>-0.06692114248400161</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.1428375052823531</v>
+        <v>0.03462950064163612</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF10" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1508827158852239</v>
+        <v>0.2402173319976812</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -6132,25 +6132,25 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.05540472024496717</v>
+        <v>0.001111593287612051</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08895143080684446</v>
+        <v>-0.1102826193400708</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1136448567996548</v>
+        <v>0.2448689779845244</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,67 +6159,67 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.03699303312441549</v>
+        <v>-0.06109390333548194</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.06991022176452612</v>
+        <v>-0.118317213545678</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01178140136480864</v>
+        <v>0.05990102900099524</v>
       </c>
       <c r="U11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.008926459609585118</v>
+        <v>-0.08081952019625631</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01436220799389488</v>
+        <v>-0.005159166439724939</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.01322699201789526</v>
+        <v>-0.03180857135565417</v>
       </c>
       <c r="AD11" t="n">
         <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01653185008956016</v>
+        <v>-0.146242924045017</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.004366665881559117</v>
+        <v>0.02679393606997117</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
@@ -6231,22 +6231,22 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.008973212011039849</v>
+        <v>0.02234935147164802</v>
       </c>
       <c r="AM11" t="n">
         <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.01569315526480149</v>
+        <v>-0.03136037861295423</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.01367214951701976</v>
+        <v>0.003433125970518289</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1153938711451974</v>
+        <v>0.2022584681956612</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
@@ -6267,25 +6267,25 @@
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.01787878461818319</v>
+        <v>-0.1793802425088967</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.02147783924078349</v>
+        <v>-0.0778709800041215</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.04234387283958466</v>
+        <v>0.01781549608877071</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,13 +6294,13 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.05423539485419909</v>
+        <v>0.002091080394419572</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.07088993894401294</v>
+        <v>-0.06049531310338922</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ11" t="n">
         <v>-0</v>
@@ -6309,37 +6309,37 @@
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.0439984694098617</v>
+        <v>0.0166954775618248</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.02614911999761512</v>
+        <v>0.06494370061543805</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.02462848970999234</v>
+        <v>-0.003852677009463982</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.04266072859301578</v>
+        <v>0.08700227029725847</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.008102824211839761</v>
+        <v>-0.03004847284499008</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.003687665916994841</v>
+        <v>-0.0596120840302558</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6360,28 +6360,28 @@
         <v>-0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.02642850495499472</v>
+        <v>-0.06768550786817001</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.004260049307465665</v>
+        <v>0.0102279727609073</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02466206814603156</v>
+        <v>0.0434279463563787</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>-0</v>
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="CM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.007458122977956908</v>
+        <v>-0.02329687057131838</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
@@ -6402,64 +6402,64 @@
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.0006786419483999593</v>
+        <v>0.09595889419233883</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.02317395392696445</v>
+        <v>0.06895874122066736</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.02001764049277187</v>
+        <v>-0.06890462123330202</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.007080366347209785</v>
+        <v>0.007130038803875816</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.02416010117408244</v>
+        <v>0.05925594604669742</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE11" t="n">
         <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.0165175536301642</v>
+        <v>-0.02047642494833745</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.02586406644362148</v>
+        <v>-0.0955212851507726</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.007079006932766817</v>
+        <v>0.05717134555870657</v>
       </c>
       <c r="DK11" t="n">
         <v>-0</v>
@@ -6474,34 +6474,34 @@
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.006781662007949998</v>
+        <v>-0.01344923766967236</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01788579728714385</v>
+        <v>-0.06585807634744219</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.008324347205209054</v>
+        <v>0.04062000882953606</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.04172477594334412</v>
+        <v>0.01409270176827759</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
@@ -6510,40 +6510,40 @@
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.01874645529140154</v>
+        <v>-0.04495200666367587</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.01161392802629558</v>
+        <v>0.02367818620302259</v>
       </c>
       <c r="EC11" t="n">
         <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.03046951967564806</v>
+        <v>-0.0390110693064973</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.007045408054830694</v>
+        <v>0.0195793374590973</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.02425673387379929</v>
+        <v>0.003155725963663686</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
         <v>-0</v>
@@ -6552,22 +6552,22 @@
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.009827443909543555</v>
+        <v>-0.01233942355497336</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.006522964190888415</v>
+        <v>0.002364471830275962</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.005877779717316957</v>
+        <v>0.07983689841976564</v>
       </c>
       <c r="EU11" t="n">
         <v>0</v>
@@ -6576,58 +6576,58 @@
         <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.02103444219215935</v>
+        <v>-0.07685724802631483</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01105978135877241</v>
+        <v>-0.005280458213963516</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.02903842041241254</v>
+        <v>0.03741108932936915</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.02336827631257295</v>
+        <v>0.1320640040835579</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.007236959987348461</v>
+        <v>-0.06257672375785009</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.01423656440811494</v>
+        <v>0.09404238662467804</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
@@ -6636,55 +6636,55 @@
         <v>0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.005684979372316152</v>
+        <v>0.03684908639976929</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.02068423631315137</v>
+        <v>-0.06688913564655337</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.008726168620858605</v>
+        <v>-0.02252705824033941</v>
       </c>
       <c r="FV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.0007518997508050961</v>
+        <v>-0.02870145490651067</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.008598198111988859</v>
+        <v>0.05832435713111219</v>
       </c>
       <c r="GE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5813243576885919</v>
+        <v>0.2140285096176106</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2206994894259464</v>
+        <v>-0.1620589676380244</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.07252604116140544</v>
+        <v>-0.02155504363874082</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -6719,16 +6719,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3569896699763817</v>
+        <v>0.2200142189123537</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2071593044659994</v>
+        <v>-0.1873635397933112</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.06665193226483974</v>
+        <v>-0.05862286185882077</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6746,133 +6746,133 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1249257747491337</v>
+        <v>0.0419436702193044</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.02355359952968996</v>
+        <v>-0.04274917345693774</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1110585249895825</v>
+        <v>-0.06472007069701625</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.03518189401378809</v>
+        <v>-0.06367616607114929</v>
       </c>
       <c r="AD12" t="n">
         <v>-0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.001077197337505317</v>
+        <v>-0.09847575367799817</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.01199750620940051</v>
+        <v>-0.06272299148959753</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.02150029386535373</v>
+        <v>0.07433204246326182</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.07057779939127096</v>
+        <v>-0.08785537101436791</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.05701923833431558</v>
+        <v>0.02079676264153217</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.5025124717972149</v>
+        <v>0.2090295542808654</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.02190687204463071</v>
+        <v>-0.06907948039734998</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1062287837388484</v>
+        <v>-0.1349588446713372</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.05983557086145651</v>
+        <v>-0.006550267135237544</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.206401151511279</v>
+        <v>-0.04782362833881886</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1324715814607463</v>
+        <v>-0.004683968080500749</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,16 +6881,16 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1583608267954703</v>
+        <v>0.00985824007954289</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.06112346576495088</v>
+        <v>0.04943320495001371</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1992811513780138</v>
+        <v>0.05537617600038331</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
@@ -6902,52 +6902,52 @@
         <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
         <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1642993282539399</v>
+        <v>0.100733829253074</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.00212385463958162</v>
+        <v>-0.07995804066813421</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.05186101998581934</v>
+        <v>-0.01379174993439551</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1117997928943105</v>
+        <v>-0.05996584714168852</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.004731869409532737</v>
+        <v>0.08514574165648765</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.01736936817915298</v>
+        <v>0.01058404678934329</v>
       </c>
       <c r="CI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ12" t="n">
         <v>0</v>
@@ -6959,28 +6959,28 @@
         <v>0</v>
       </c>
       <c r="CM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.01068045688767222</v>
+        <v>-0.04769037141456656</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.1212422279322519</v>
+        <v>0.1385422200882636</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.111511230346818</v>
+        <v>0.02258257277255022</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
         <v>-0</v>
@@ -6989,43 +6989,43 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.07739655762398902</v>
+        <v>-0.05732712844428756</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.04811590700710487</v>
+        <v>0.08833178482097961</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.02580664016101752</v>
+        <v>0.0198981360659001</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.04762004907848635</v>
+        <v>-0.04878290384335696</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.06158190868520314</v>
+        <v>0.02118362689974244</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.03325450218359662</v>
+        <v>-0.02851880885602913</v>
       </c>
       <c r="DJ12" t="n">
         <v>-0</v>
@@ -7040,28 +7040,28 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.08595384562032246</v>
+        <v>-0.03986818059830998</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.004288517580598857</v>
+        <v>-0.01274351768998171</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.04198705855323432</v>
+        <v>-0.008623886766911514</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
@@ -7070,19 +7070,19 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.1167563420244909</v>
+        <v>0.01292444487786096</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.01496696756663771</v>
+        <v>0.07666161945503448</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.04456813443004735</v>
+        <v>-0.04614350998299566</v>
       </c>
       <c r="EB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC12" t="n">
         <v>-0</v>
@@ -7091,85 +7091,85 @@
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.09548131834028595</v>
+        <v>-0.03981101147317752</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.01601281293796111</v>
+        <v>0.06031493344383522</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.06163472843071433</v>
+        <v>0.0539949693488185</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.002499175480886409</v>
+        <v>-0.001278404828596262</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>-0.008703273729854412</v>
+        <v>0.0536409264515467</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02338733960352353</v>
+        <v>-0.02447356474861561</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX12" t="n">
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.07610308434348266</v>
+        <v>-0.06241191557339784</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.003396274756274597</v>
+        <v>0.1073159268335619</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.009733433973316323</v>
+        <v>-0.001413111506326092</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF12" t="n">
         <v>0</v>
@@ -7178,16 +7178,16 @@
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.08058879776498599</v>
+        <v>0.09852467641528358</v>
       </c>
       <c r="FI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.00641199004439016</v>
+        <v>0.06408232173334319</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.05149287077661532</v>
+        <v>-0.02704003936808545</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7199,28 +7199,28 @@
         <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.05826825703075308</v>
+        <v>0.0413641989796804</v>
       </c>
       <c r="FR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.01198161159234575</v>
+        <v>0.1080327000434127</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.08264678248169126</v>
+        <v>-0.04951974498167596</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
         <v>-0</v>
@@ -7229,28 +7229,28 @@
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.07896142475276292</v>
+        <v>-0.009315359319941627</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.132879181348353</v>
+        <v>0.02432941102280659</v>
       </c>
       <c r="GC12" t="n">
         <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
         <v>-0</v>
@@ -7261,7 +7261,7 @@
         <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.9555535467151666</v>
+        <v>-0.3533002079028263</v>
       </c>
       <c r="C13" t="n">
         <v>-0</v>
@@ -7270,13 +7270,13 @@
         <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.125218400974022</v>
+        <v>0.1283585112200805</v>
       </c>
       <c r="F13" t="n">
-        <v>1.367357707842619</v>
+        <v>0.5584751156981523</v>
       </c>
       <c r="G13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -7285,10 +7285,10 @@
         <v>-0</v>
       </c>
       <c r="J13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.774964630484031</v>
+        <v>-0.541171906617035</v>
       </c>
       <c r="L13" t="n">
         <v>-0</v>
@@ -7297,10 +7297,10 @@
         <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.08593641735988644</v>
+        <v>0.1752026624678895</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9513003471920908</v>
+        <v>0.5923779444512263</v>
       </c>
       <c r="P13" t="n">
         <v>-0</v>
@@ -7309,52 +7309,52 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.08767046504047085</v>
+        <v>-0.1037396363313098</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>-0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.255751955271979</v>
+        <v>0.1335945490888242</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1525096043649294</v>
+        <v>0.09325074991965922</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.0365806195114871</v>
+        <v>0.01487611978664904</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>-0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.193784556180716</v>
+        <v>0.1787230598845983</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.136856267870123</v>
+        <v>-0.03626830346152047</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,13 +7363,13 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
         <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.106279521899657</v>
+        <v>-0.06010904197959577</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         <v>-0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.04253660065987656</v>
+        <v>0.02677046183071049</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.2565428489980843</v>
+        <v>0.08494498845276764</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -7393,37 +7393,37 @@
         <v>-0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0.6172717534061476</v>
+        <v>-0.6818937221120029</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW13" t="n">
         <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.2705298344331309</v>
+        <v>0.08214408961948282</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.8951261879568482</v>
+        <v>0.3424625867890921</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>-0.2789822097179999</v>
+        <v>0.1842094098689358</v>
       </c>
       <c r="BE13" t="n">
         <v>-0</v>
@@ -7432,10 +7432,10 @@
         <v>-0</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.1325191045465678</v>
+        <v>0.1129157665574255</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.341250828619303</v>
+        <v>0.03919596040593061</v>
       </c>
       <c r="BI13" t="n">
         <v>-0</v>
@@ -7444,52 +7444,52 @@
         <v>0</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>-0.3118136950174849</v>
+        <v>-0.1794629255678651</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.1115819091716627</v>
+        <v>-0.1475984104975039</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.02734112332789938</v>
+        <v>-0.1335762630905444</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT13" t="n">
         <v>-0</v>
       </c>
       <c r="BU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0.3985786115602167</v>
+        <v>-0.3068061675727154</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>-0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.08213475946453966</v>
+        <v>0.007568137216141973</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.3854074217352527</v>
+        <v>0.2026751854423259</v>
       </c>
       <c r="CA13" t="n">
         <v>0</v>
@@ -7504,22 +7504,22 @@
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.1664524391208402</v>
+        <v>0.1047180473073995</v>
       </c>
       <c r="CF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG13" t="n">
         <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.02167547117803665</v>
+        <v>-0.06922820647789719</v>
       </c>
       <c r="CI13" t="n">
-        <v>-0.2299443871168447</v>
+        <v>-0.147455566111848</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
@@ -7531,7 +7531,7 @@
         <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.04461671217303093</v>
+        <v>0.1984712269322874</v>
       </c>
       <c r="CO13" t="n">
         <v>0</v>
@@ -7540,16 +7540,16 @@
         <v>0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.228126154058156</v>
+        <v>-0.03158455191819531</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.02552499353990513</v>
+        <v>0.007798438236878267</v>
       </c>
       <c r="CS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU13" t="n">
         <v>0</v>
@@ -7558,22 +7558,22 @@
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.1385072600200643</v>
+        <v>0.09824052826777047</v>
       </c>
       <c r="CX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY13" t="n">
         <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.02132292414102758</v>
+        <v>-0.06746262848456921</v>
       </c>
       <c r="DA13" t="n">
-        <v>-0.2484861342905257</v>
+        <v>-0.1692339418255203</v>
       </c>
       <c r="DB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
@@ -7582,49 +7582,49 @@
         <v>-0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.2395404847638643</v>
+        <v>0.1115678090768223</v>
       </c>
       <c r="DG13" t="n">
         <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.2939200123485097</v>
+        <v>0.1141473448940579</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.003028341296505732</v>
+        <v>-0.01179284602614442</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>-0</v>
       </c>
       <c r="DM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN13" t="n">
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0383313838986394</v>
+        <v>-0.01895351364657017</v>
       </c>
       <c r="DP13" t="n">
         <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.05398197819079133</v>
+        <v>0.05685659910989263</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.1432666533808165</v>
+        <v>-0.1433323187563683</v>
       </c>
       <c r="DT13" t="n">
         <v>0</v>
@@ -7633,25 +7633,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.1286753574867674</v>
+        <v>0.1170513750861301</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.1064783166537736</v>
+        <v>0.01348738087853794</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.1019188304297612</v>
+        <v>-0.01317884500368069</v>
       </c>
       <c r="EC13" t="n">
         <v>0</v>
@@ -7660,31 +7660,31 @@
         <v>-0</v>
       </c>
       <c r="EE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.1043654927206298</v>
+        <v>0.04332721976141553</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.05874249858191107</v>
+        <v>-0.03134420921569546</v>
       </c>
       <c r="EK13" t="n">
-        <v>-0.1857520990892341</v>
+        <v>-0.06111526526512318</v>
       </c>
       <c r="EL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
         <v>0</v>
@@ -7693,7 +7693,7 @@
         <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.09569497589024525</v>
+        <v>0.04958670946011468</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
@@ -7702,25 +7702,25 @@
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.008703144792652799</v>
+        <v>-0.05905340457962627</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.002452998929811908</v>
+        <v>0.147769981378384</v>
       </c>
       <c r="EU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV13" t="n">
         <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX13" t="n">
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.1321316036627264</v>
+        <v>0.121034147440436</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
@@ -7729,13 +7729,13 @@
         <v>0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.0492038552903505</v>
+        <v>-0.02740460909330773</v>
       </c>
       <c r="FC13" t="n">
-        <v>-0.2257031928486266</v>
+        <v>-0.1478208679297496</v>
       </c>
       <c r="FD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
@@ -7747,7 +7747,7 @@
         <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.0147379497163268</v>
+        <v>-0.083775260201131</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,10 +7756,10 @@
         <v>0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.0152848375093764</v>
+        <v>0.06975006930206748</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.1619539842595783</v>
+        <v>-0.08667578970839165</v>
       </c>
       <c r="FM13" t="n">
         <v>-0</v>
@@ -7768,52 +7768,52 @@
         <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.01578419601728682</v>
+        <v>0.03449667826520292</v>
       </c>
       <c r="FR13" t="n">
         <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.1171188790328716</v>
+        <v>0.1502937213230972</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.1960341491796673</v>
+        <v>0.1790597287533324</v>
       </c>
       <c r="FV13" t="n">
         <v>0</v>
       </c>
       <c r="FW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX13" t="n">
         <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.03153613549508923</v>
+        <v>0.04596655001965494</v>
       </c>
       <c r="GA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB13" t="n">
         <v>0</v>
       </c>
       <c r="GC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.1265500728807336</v>
+        <v>-0.07512856400080017</v>
       </c>
       <c r="GE13" t="n">
         <v>0</v>
@@ -7822,12 +7822,12 @@
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.1579309657606398</v>
+        <v>0.3395026015448797</v>
       </c>
       <c r="B14" t="n">
         <v>-0</v>
@@ -7839,13 +7839,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.002062509904998334</v>
+        <v>5.031951349659168e-05</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1440615630925162</v>
+        <v>-0.1375987411705322</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
         <v>-0</v>
@@ -7854,10 +7854,10 @@
         <v>-0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1233197493734981</v>
+        <v>0.3116027338226297</v>
       </c>
       <c r="K14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -7866,40 +7866,40 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.01531587392365156</v>
+        <v>-0.150273118281725</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1081050802752104</v>
+        <v>-0.2051877834276671</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>-0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02037933682254647</v>
+        <v>-0.03456355767217349</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.01996452474508568</v>
+        <v>0.03227011457483955</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.04084137734115367</v>
+        <v>-0.02549758402511463</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -7908,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.02430063161776922</v>
+        <v>0.02669716617710559</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -7917,16 +7917,16 @@
         <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.01015817872023107</v>
+        <v>-0.05909778891144793</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.01878738735423515</v>
+        <v>0.09647983708093698</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -7935,49 +7935,49 @@
         <v>-0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.02660686185573689</v>
+        <v>0.0412893496044962</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.02169268939640987</v>
+        <v>0.0375131562887402</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.01854946827056193</v>
+        <v>0.02135514439549495</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.08048047464782969</v>
+        <v>0.1256104307242744</v>
       </c>
       <c r="AU14" t="n">
         <v>-0</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.04839249995448342</v>
+        <v>-0.005310389798564583</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.06952785216480141</v>
+        <v>-0.1122869878121553</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -7989,22 +7989,22 @@
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.03912543410912706</v>
+        <v>0.1127501272889474</v>
       </c>
       <c r="BD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.01978195399292558</v>
+        <v>-0.02715267139134464</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0.06206423708270363</v>
+        <v>0.07047526441116896</v>
       </c>
       <c r="BI14" t="n">
         <v>0</v>
@@ -8016,52 +8016,52 @@
         <v>-0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0.0009339359621069522</v>
+        <v>-0.05993342263963333</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.02317516172825269</v>
+        <v>-0.154309370633205</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.005510130071806345</v>
+        <v>0.04613003827270573</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.04272999750064014</v>
+        <v>0.05848808710617623</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
       </c>
       <c r="BW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.009650314691324205</v>
+        <v>-0.09802971521207755</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0.04152762580788315</v>
+        <v>-0.05682214246312278</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB14" t="n">
         <v>0</v>
@@ -8070,25 +8070,25 @@
         <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0.02950793266379362</v>
+        <v>-0.07974596159020114</v>
       </c>
       <c r="CE14" t="n">
         <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.003119697467546191</v>
+        <v>0.0357180108896093</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.03210219308404522</v>
+        <v>0.04092891997628759</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>0</v>
@@ -8097,34 +8097,34 @@
         <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0.003887501391928498</v>
+        <v>-0.02830392360850174</v>
       </c>
       <c r="CN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.03765491202443046</v>
+        <v>0.2036461302788827</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.006480832166932005</v>
+        <v>-0.09116718205522145</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
         <v>-0</v>
       </c>
       <c r="CU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0.02748902616889345</v>
+        <v>-0.08828320624860436</v>
       </c>
       <c r="CW14" t="n">
         <v>-0</v>
@@ -8136,64 +8136,64 @@
         <v>-0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.006438022574553357</v>
+        <v>0.03822012176900542</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.02715361035583444</v>
+        <v>0.05532172916999099</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
         <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE14" t="n">
-        <v>-0.0003229328054935052</v>
+        <v>-0.002293309109758107</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.003639453667989901</v>
+        <v>-0.01222602261182273</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.02504617243515229</v>
+        <v>0.02021265861381678</v>
       </c>
       <c r="DK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
         <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0.01165685776789508</v>
+        <v>-0.03832120989353538</v>
       </c>
       <c r="DO14" t="n">
         <v>0</v>
       </c>
       <c r="DP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ14" t="n">
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.005441236865295638</v>
+        <v>-0.008711802460212317</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0332996145674316</v>
+        <v>0.07290878640664013</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
@@ -8202,13 +8202,13 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>-0.009573496140179692</v>
+        <v>-0.0007401236901088175</v>
       </c>
       <c r="DX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY14" t="n">
         <v>-0</v>
@@ -8217,37 +8217,37 @@
         <v>0</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.006375622279817778</v>
+        <v>0.2134900589116847</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.01023388080882538</v>
+        <v>0.04103592815788894</v>
       </c>
       <c r="EC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED14" t="n">
         <v>-0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0.02497385562171606</v>
+        <v>-0.003985438414683904</v>
       </c>
       <c r="EG14" t="n">
         <v>0</v>
       </c>
       <c r="EH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI14" t="n">
         <v>0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.01184644214678479</v>
+        <v>-0.01278295147820323</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.01918113999791521</v>
+        <v>0.05479012062848418</v>
       </c>
       <c r="EL14" t="n">
         <v>-0</v>
@@ -8256,10 +8256,10 @@
         <v>0</v>
       </c>
       <c r="EN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.008675408975855503</v>
+        <v>0.06427839405037968</v>
       </c>
       <c r="EP14" t="n">
         <v>0</v>
@@ -8268,13 +8268,13 @@
         <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.01691449656249501</v>
+        <v>0.04933995629361376</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.004402519263486972</v>
+        <v>0.01532645209140761</v>
       </c>
       <c r="EU14" t="n">
         <v>0</v>
@@ -8283,10 +8283,10 @@
         <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0.02585173574717364</v>
+        <v>-0.07920273255707154</v>
       </c>
       <c r="EY14" t="n">
         <v>0</v>
@@ -8298,13 +8298,13 @@
         <v>0</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.01051616013090552</v>
+        <v>0.03974485033865238</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.02741666215149489</v>
+        <v>0.05466035745958849</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
@@ -8313,7 +8313,7 @@
         <v>0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0.01411831644716053</v>
+        <v>-0.09904359305157003</v>
       </c>
       <c r="FH14" t="n">
         <v>-0</v>
@@ -8325,55 +8325,55 @@
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.001086091336808162</v>
+        <v>0.0004306745533487138</v>
       </c>
       <c r="FL14" t="n">
-        <v>-0.0007414155784733195</v>
+        <v>0.01996063254442207</v>
       </c>
       <c r="FM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>-0.01406957366843699</v>
+        <v>-0.1517896920271032</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.005908819036342376</v>
+        <v>0.007813253424440746</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.03298655549764764</v>
+        <v>0.1436246770624217</v>
       </c>
       <c r="FV14" t="n">
         <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.002011294494542216</v>
+        <v>0.02881906034122671</v>
       </c>
       <c r="FZ14" t="n">
         <v>-0</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
         <v>-0</v>
@@ -8382,13 +8382,13 @@
         <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.006441024939235725</v>
+        <v>0.03089850698238748</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
         <v>0</v>
